--- a/doc/MaterialImportTemplate2.xlsx
+++ b/doc/MaterialImportTemplate2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SourceCode\CS\PartsManager\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20F1EFE-688F-41A3-86E0-D2AC00E93967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962D1A06-4AD7-4DB1-8812-2D4C528BEE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,10 +55,6 @@
     <t>附件2檔名 (Attachment2)</t>
   </si>
   <si>
-    <t>TEST1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TB&amp;C</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -67,10 +63,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TEST2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DELTA</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -79,14 +71,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TEST3</t>
-  </si>
-  <si>
     <t>Innolux</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>test4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEST6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEST7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TEST8</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -497,13 +498,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>1233524</v>
+        <v>321312</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -515,24 +516,24 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" t="s">
         <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>1235123</v>
+        <v>123213</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>60</v>
@@ -544,24 +545,24 @@
         <v>20</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>332423</v>
+        <v>2353353</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -573,13 +574,13 @@
         <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
